--- a/Vulnerability Test Results/test-cases.xlsx
+++ b/Vulnerability Test Results/test-cases.xlsx
@@ -644,7 +644,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DentAI — Complete Test Case Catalog</t>
+          <t>DentAI â€” Complete Test Case Catalog</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Brute force — 10 rapid attempts</t>
+          <t>Brute force â€” 10 rapid attempts</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Brute force — 100 rapid attempts</t>
+          <t>Brute force â€” 100 rapid attempts</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Forgot password — valid email</t>
+          <t>Forgot password â€” valid email</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Forgot password — token NOT in response</t>
+          <t>Forgot password â€” token NOT in response</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Forgot password — unknown email (no enumeration)</t>
+          <t>Forgot password â€” unknown email (no enumeration)</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Reset token reuse — second use fails</t>
+          <t>Reset token reuse â€” second use fails</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Change password — correct old password</t>
+          <t>Change password â€” correct old password</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Change password — wrong old password</t>
+          <t>Change password â€” wrong old password</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Change password — IDOR different user</t>
+          <t>Change password â€” IDOR different user</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>JWT expiry is set and ≤24 hours</t>
+          <t>JWT expiry is set and â‰¤24 hours</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>IDOR — read another doctor profile</t>
+          <t>IDOR â€” read another doctor profile</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>IDOR — update another doctor profile</t>
+          <t>IDOR â€” update another doctor profile</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>IDOR — fetch another doctor credentials</t>
+          <t>IDOR â€” fetch another doctor credentials</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>IDOR — download another patient STL</t>
+          <t>IDOR â€” download another patient STL</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>IDOR — trigger analysis on another user scan</t>
+          <t>IDOR â€” trigger analysis on another user scan</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>IDOR — export another user DICOM</t>
+          <t>IDOR â€” export another user DICOM</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>IDOR — change another user password</t>
+          <t>IDOR â€” change another user password</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>IDOR — negative scan ID</t>
+          <t>IDOR â€” negative scan ID</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>IDOR — zero scan ID</t>
+          <t>IDOR â€” zero scan ID</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>IDOR — non-numeric scan ID</t>
+          <t>IDOR â€” non-numeric scan ID</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>IDOR — overflow scan ID</t>
+          <t>IDOR â€” overflow scan ID</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>JWT RS256→HS256 algorithm confusion</t>
+          <t>JWT RS256â†’HS256 algorithm confusion</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>JWT role tampering — elevate to admin</t>
+          <t>JWT role tampering â€” elevate to admin</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>Scan IDs 1–100</t>
+          <t>Scan IDs 1â€“100</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Doctor scope — GET /scans returns only own data</t>
+          <t>Doctor scope â€” GET /scans returns only own data</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Mass assignment — inject is_admin=true on signup</t>
+          <t>Mass assignment â€” inject is_admin=true on signup</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>IDOR — sequential doctor ID profile enumeration</t>
+          <t>IDOR â€” sequential doctor ID profile enumeration</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>POST /fetch_profile id=1–100 no auth</t>
+          <t>POST /fetch_profile id=1â€“100 no auth</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>IDs 1–100 no token</t>
+          <t>IDs 1â€“100 no token</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>Privilege escalation — doctor accessing admin function</t>
+          <t>Privilege escalation â€” doctor accessing admin function</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>SQLi login email — classic OR bypass</t>
+          <t>SQLi login email â€” classic OR bypass</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>SQLi login email — comment bypass</t>
+          <t>SQLi login email â€” comment bypass</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>SQLi login email — UNION SELECT</t>
+          <t>SQLi login email â€” UNION SELECT</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>SQLi login — stacked queries DROP TABLE</t>
+          <t>SQLi login â€” stacked queries DROP TABLE</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>SQLi login — time-based blind (SLEEP)</t>
+          <t>SQLi login â€” time-based blind (SLEEP)</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>SQLi signup name — Bobby Tables</t>
+          <t>SQLi signup name â€” Bobby Tables</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>Path traversal filename — ../ sequences</t>
+          <t>Path traversal filename â€” ../ sequences</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Path traversal — URL encoded %2F</t>
+          <t>Path traversal â€” URL encoded %2F</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Path traversal — double encoded %252F</t>
+          <t>Path traversal â€” double encoded %252F</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Path traversal — Windows backslash</t>
+          <t>Path traversal â€” Windows backslash</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Path traversal — null byte in filename</t>
+          <t>Path traversal â€” null byte in filename</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Zip slip — entry with ../ path</t>
+          <t>Zip slip â€” entry with ../ path</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>Zip slip — absolute path /etc entry</t>
+          <t>Zip slip â€” absolute path /etc entry</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Zip slip — Windows absolute path C:\</t>
+          <t>Zip slip â€” Windows absolute path C:\</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>Template injection — Jinja2 {{config}}</t>
+          <t>Template injection â€” Jinja2 {{config}}</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Template injection — arithmetic {{7*7}}</t>
+          <t>Template injection â€” arithmetic {{7*7}}</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Zip bomb — 1000 small files</t>
+          <t>Zip bomb â€” 1000 small files</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>Zip bomb — deeply nested ZIPs</t>
+          <t>Zip bomb â€” deeply nested ZIPs</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Path traversal results-img — encoded</t>
+          <t>Path traversal results-img â€” encoded</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Upload MIME mismatch — Python script as .dcm</t>
+          <t>Upload MIME mismatch â€” Python script as .dcm</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>Path traversal in results-img — UNC path</t>
+          <t>Path traversal in results-img â€” UNC path</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>SQL injection in batch — INSERT via signup</t>
+          <t>SQL injection in batch â€” INSERT via signup</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="F143" s="8" t="inlineStr">
         <is>
-          <t>POST /login email=dr😀@test.com</t>
+          <t>POST /login email=drðŸ˜€@test.com</t>
         </is>
       </c>
       <c r="G143" s="8" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>Upload MIME mismatch — Python as DICOM</t>
+          <t>Upload MIME mismatch â€” Python as DICOM</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t>Cyrillic о in email</t>
+          <t>Cyrillic Ð¾ in email</t>
         </is>
       </c>
       <c r="H165" s="8" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>Race condition — analyze same scan twice</t>
+          <t>Race condition â€” analyze same scan twice</t>
         </is>
       </c>
       <c r="D177" s="8" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>Token replay — use used reset token again</t>
+          <t>Token replay â€” use used reset token again</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>Concurrent analysis — 10 simultaneous</t>
+          <t>Concurrent analysis â€” 10 simultaneous</t>
         </is>
       </c>
       <c r="D183" s="8" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>Cross-user workflow — doctor 1 upload doctor 2 analyze</t>
+          <t>Cross-user workflow â€” doctor 1 upload doctor 2 analyze</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C191" s="8" t="inlineStr">
         <is>
-          <t>STL region export — all 4 regions available</t>
+          <t>STL region export â€” all 4 regions available</t>
         </is>
       </c>
       <c r="D191" s="8" t="inlineStr">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>CORS — specific origin allowed</t>
+          <t>CORS â€” specific origin allowed</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
@@ -11484,7 +11484,7 @@
       </c>
       <c r="C211" s="8" t="inlineStr">
         <is>
-          <t>CORS — unknown origin rejected</t>
+          <t>CORS â€” unknown origin rejected</t>
         </is>
       </c>
       <c r="D211" s="8" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>CORS — wildcard not used</t>
+          <t>CORS â€” wildcard not used</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="H223" s="8" t="inlineStr">
         <is>
-          <t>Permission denied — no DROP privilege</t>
+          <t>Permission denied â€” no DROP privilege</t>
         </is>
       </c>
       <c r="I223" s="9" t="inlineStr">
@@ -12373,7 +12373,7 @@
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>Verify HTTP → HTTPS redirect</t>
+          <t>Verify HTTP â†’ HTTPS redirect</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>POST /login — valid credentials</t>
+          <t>POST /login â€” valid credentials</t>
         </is>
       </c>
       <c r="D234" s="5" t="inlineStr">
@@ -12732,7 +12732,7 @@
       </c>
       <c r="C235" s="8" t="inlineStr">
         <is>
-          <t>POST /login — wrong password</t>
+          <t>POST /login â€” wrong password</t>
         </is>
       </c>
       <c r="D235" s="8" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>POST /login — missing email field</t>
+          <t>POST /login â€” missing email field</t>
         </is>
       </c>
       <c r="D236" s="5" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C237" s="8" t="inlineStr">
         <is>
-          <t>POST /login — missing password field</t>
+          <t>POST /login â€” missing password field</t>
         </is>
       </c>
       <c r="D237" s="8" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>POST /signup — valid new registration</t>
+          <t>POST /signup â€” valid new registration</t>
         </is>
       </c>
       <c r="D238" s="5" t="inlineStr">
@@ -12940,7 +12940,7 @@
       </c>
       <c r="C239" s="8" t="inlineStr">
         <is>
-          <t>POST /signup — duplicate email returns error</t>
+          <t>POST /signup â€” duplicate email returns error</t>
         </is>
       </c>
       <c r="D239" s="8" t="inlineStr">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>POST /signup — response has no password field</t>
+          <t>POST /signup â€” response has no password field</t>
         </is>
       </c>
       <c r="D240" s="5" t="inlineStr">
@@ -13044,7 +13044,7 @@
       </c>
       <c r="C241" s="8" t="inlineStr">
         <is>
-          <t>POST /forgot-password — valid email</t>
+          <t>POST /forgot-password â€” valid email</t>
         </is>
       </c>
       <c r="D241" s="8" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>POST /forgot-password — unknown email</t>
+          <t>POST /forgot-password â€” unknown email</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="C243" s="8" t="inlineStr">
         <is>
-          <t>POST /reset-password — valid token+password</t>
+          <t>POST /reset-password â€” valid token+password</t>
         </is>
       </c>
       <c r="D243" s="8" t="inlineStr">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>POST /reset-password — invalid token</t>
+          <t>POST /reset-password â€” invalid token</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="C245" s="8" t="inlineStr">
         <is>
-          <t>POST /fetch_profile — own profile</t>
+          <t>POST /fetch_profile â€” own profile</t>
         </is>
       </c>
       <c r="D245" s="8" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>POST /fetch_profile — response has no password</t>
+          <t>POST /fetch_profile â€” response has no password</t>
         </is>
       </c>
       <c r="D246" s="5" t="inlineStr">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C247" s="8" t="inlineStr">
         <is>
-          <t>POST /update_profile — valid update</t>
+          <t>POST /update_profile â€” valid update</t>
         </is>
       </c>
       <c r="D247" s="8" t="inlineStr">
@@ -13408,7 +13408,7 @@
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>POST /update_profile — then fetch verifies change</t>
+          <t>POST /update_profile â€” then fetch verifies change</t>
         </is>
       </c>
       <c r="D248" s="5" t="inlineStr">
@@ -13460,7 +13460,7 @@
       </c>
       <c r="C249" s="8" t="inlineStr">
         <is>
-          <t>POST /change_password — success</t>
+          <t>POST /change_password â€” success</t>
         </is>
       </c>
       <c r="D249" s="8" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>POST /change_password — login with new password</t>
+          <t>POST /change_password â€” login with new password</t>
         </is>
       </c>
       <c r="D250" s="5" t="inlineStr">
@@ -13564,7 +13564,7 @@
       </c>
       <c r="C251" s="8" t="inlineStr">
         <is>
-          <t>POST /change_password — old password no longer works</t>
+          <t>POST /change_password â€” old password no longer works</t>
         </is>
       </c>
       <c r="D251" s="8" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>POST /add_credential — valid credential</t>
+          <t>POST /add_credential â€” valid credential</t>
         </is>
       </c>
       <c r="D252" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="C253" s="8" t="inlineStr">
         <is>
-          <t>POST /fetch_credentials — returns list</t>
+          <t>POST /fetch_credentials â€” returns list</t>
         </is>
       </c>
       <c r="D253" s="8" t="inlineStr">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>POST /upload — .dcm file success</t>
+          <t>POST /upload â€” .dcm file success</t>
         </is>
       </c>
       <c r="D254" s="5" t="inlineStr">
@@ -13772,7 +13772,7 @@
       </c>
       <c r="C255" s="8" t="inlineStr">
         <is>
-          <t>POST /upload — .nii.gz file success</t>
+          <t>POST /upload â€” .nii.gz file success</t>
         </is>
       </c>
       <c r="D255" s="8" t="inlineStr">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>POST /upload — .zip of DICOMs success</t>
+          <t>POST /upload â€” .zip of DICOMs success</t>
         </is>
       </c>
       <c r="D256" s="5" t="inlineStr">
@@ -13876,7 +13876,7 @@
       </c>
       <c r="C257" s="8" t="inlineStr">
         <is>
-          <t>POST /upload — unsupported type rejected</t>
+          <t>POST /upload â€” unsupported type rejected</t>
         </is>
       </c>
       <c r="D257" s="8" t="inlineStr">
@@ -13928,7 +13928,7 @@
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>POST /upload — response has scan_id</t>
+          <t>POST /upload â€” response has scan_id</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="C259" s="8" t="inlineStr">
         <is>
-          <t>GET /scans — returns array</t>
+          <t>GET /scans â€” returns array</t>
         </is>
       </c>
       <c r="D259" s="8" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>GET /scans — limited to 50 results</t>
+          <t>GET /scans â€” limited to 50 results</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="C261" s="8" t="inlineStr">
         <is>
-          <t>POST /analyze/{scan_id} — success</t>
+          <t>POST /analyze/{scan_id} â€” success</t>
         </is>
       </c>
       <c r="D261" s="8" t="inlineStr">
@@ -14136,7 +14136,7 @@
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>POST /analyze/{scan_id} — invalid id</t>
+          <t>POST /analyze/{scan_id} â€” invalid id</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="C263" s="8" t="inlineStr">
         <is>
-          <t>GET /stl/{scan_id} — success</t>
+          <t>GET /stl/{scan_id} â€” success</t>
         </is>
       </c>
       <c r="D263" s="8" t="inlineStr">
@@ -14240,7 +14240,7 @@
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>GET /stl/{scan_id} — not found</t>
+          <t>GET /stl/{scan_id} â€” not found</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr">
@@ -14292,7 +14292,7 @@
       </c>
       <c r="C265" s="8" t="inlineStr">
         <is>
-          <t>GET /stl-region/{id}/{region} — condylar L</t>
+          <t>GET /stl-region/{id}/{region} â€” condylar L</t>
         </is>
       </c>
       <c r="D265" s="8" t="inlineStr">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>GET /stl-region/{id}/{region} — condylar R</t>
+          <t>GET /stl-region/{id}/{region} â€” condylar R</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="C267" s="8" t="inlineStr">
         <is>
-          <t>GET /stl-region/{id}/{region} — coronoid L</t>
+          <t>GET /stl-region/{id}/{region} â€” coronoid L</t>
         </is>
       </c>
       <c r="D267" s="8" t="inlineStr">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>GET /stl-region/{id}/{region} — coronoid R</t>
+          <t>GET /stl-region/{id}/{region} â€” coronoid R</t>
         </is>
       </c>
       <c r="D268" s="5" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="C269" s="8" t="inlineStr">
         <is>
-          <t>GET /export-dicom/{id}/{region} — success</t>
+          <t>GET /export-dicom/{id}/{region} â€” success</t>
         </is>
       </c>
       <c r="D269" s="8" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>GET /results-img — valid path</t>
+          <t>GET /results-img â€” valid path</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
@@ -14604,7 +14604,7 @@
       </c>
       <c r="C271" s="8" t="inlineStr">
         <is>
-          <t>GET /results-img — missing file</t>
+          <t>GET /results-img â€” missing file</t>
         </is>
       </c>
       <c r="D271" s="8" t="inlineStr">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>GET /health — returns 200</t>
+          <t>GET /health â€” returns 200</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
@@ -14708,7 +14708,7 @@
       </c>
       <c r="C273" s="8" t="inlineStr">
         <is>
-          <t>GET /health — response has version field</t>
+          <t>GET /health â€” response has version field</t>
         </is>
       </c>
       <c r="D273" s="8" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="C277" s="8" t="inlineStr">
         <is>
-          <t>POST /fetch_profile — all fields present</t>
+          <t>POST /fetch_profile â€” all fields present</t>
         </is>
       </c>
       <c r="D277" s="8" t="inlineStr">
@@ -14968,7 +14968,7 @@
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>POST /add_credential — then verify in fetch</t>
+          <t>POST /add_credential â€” then verify in fetch</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="C279" s="8" t="inlineStr">
         <is>
-          <t>POST /login — response has doctor id</t>
+          <t>POST /login â€” response has doctor id</t>
         </is>
       </c>
       <c r="D279" s="8" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>POST /login — response has doctor name</t>
+          <t>POST /login â€” response has doctor name</t>
         </is>
       </c>
       <c r="D280" s="5" t="inlineStr">
@@ -15124,7 +15124,7 @@
       </c>
       <c r="C281" s="8" t="inlineStr">
         <is>
-          <t>GET /scans — response has scan metadata</t>
+          <t>GET /scans â€” response has scan metadata</t>
         </is>
       </c>
       <c r="D281" s="8" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>POST /analyze — response has results</t>
+          <t>POST /analyze â€” response has results</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C283" s="8" t="inlineStr">
         <is>
-          <t>POST /upload — ZIP extracted correctly</t>
+          <t>POST /upload â€” ZIP extracted correctly</t>
         </is>
       </c>
       <c r="D283" s="8" t="inlineStr">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>POST /forgot-password — 400 on missing email</t>
+          <t>POST /forgot-password â€” 400 on missing email</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="C285" s="8" t="inlineStr">
         <is>
-          <t>POST /reset-password — 422 on missing fields</t>
+          <t>POST /reset-password â€” 422 on missing fields</t>
         </is>
       </c>
       <c r="D285" s="8" t="inlineStr">
@@ -15384,7 +15384,7 @@
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>POST /change_password — 422 on missing fields</t>
+          <t>POST /change_password â€” 422 on missing fields</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="C287" s="8" t="inlineStr">
         <is>
-          <t>POST /upload — scan listed in GET /scans after</t>
+          <t>POST /upload â€” scan listed in GET /scans after</t>
         </is>
       </c>
       <c r="D287" s="8" t="inlineStr">
@@ -15488,7 +15488,7 @@
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>POST /analyze — STL available after analysis</t>
+          <t>POST /analyze â€” STL available after analysis</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
@@ -15644,7 +15644,7 @@
       </c>
       <c r="C291" s="8" t="inlineStr">
         <is>
-          <t>POST /login — 200 with success=false on wrong creds</t>
+          <t>POST /login â€” 200 with success=false on wrong creds</t>
         </is>
       </c>
       <c r="D291" s="8" t="inlineStr">
@@ -15696,7 +15696,7 @@
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>POST /signup — 200 with success=false on duplicate</t>
+          <t>POST /signup â€” 200 with success=false on duplicate</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
@@ -15748,7 +15748,7 @@
       </c>
       <c r="C293" s="8" t="inlineStr">
         <is>
-          <t>POST /upload — filename stored without path</t>
+          <t>POST /upload â€” filename stored without path</t>
         </is>
       </c>
       <c r="D293" s="8" t="inlineStr">
@@ -15800,7 +15800,7 @@
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>POST /analyze — returns 404 for missing scan</t>
+          <t>POST /analyze â€” returns 404 for missing scan</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
@@ -15852,7 +15852,7 @@
       </c>
       <c r="C295" s="8" t="inlineStr">
         <is>
-          <t>GET /stl-region — 400 for invalid region</t>
+          <t>GET /stl-region â€” 400 for invalid region</t>
         </is>
       </c>
       <c r="D295" s="8" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>POST /fetch_profile — 404 for non-existent id</t>
+          <t>POST /fetch_profile â€” 404 for non-existent id</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
@@ -16008,7 +16008,7 @@
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>POST /login — no token on failure</t>
+          <t>POST /login â€” no token on failure</t>
         </is>
       </c>
       <c r="D298" s="5" t="inlineStr">
@@ -16060,7 +16060,7 @@
       </c>
       <c r="C299" s="8" t="inlineStr">
         <is>
-          <t>POST /upload — accepts .nii file (no .gz)</t>
+          <t>POST /upload â€” accepts .nii file (no .gz)</t>
         </is>
       </c>
       <c r="D299" s="8" t="inlineStr">
@@ -16112,7 +16112,7 @@
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
-          <t>GET /scans — empty array when no scans</t>
+          <t>GET /scans â€” empty array when no scans</t>
         </is>
       </c>
       <c r="D300" s="5" t="inlineStr">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="C301" s="8" t="inlineStr">
         <is>
-          <t>POST /fetch_credentials — empty list when none</t>
+          <t>POST /fetch_credentials â€” empty list when none</t>
         </is>
       </c>
       <c r="D301" s="8" t="inlineStr">
@@ -16216,7 +16216,7 @@
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
-          <t>POST /update_profile — partial update (name only)</t>
+          <t>POST /update_profile â€” partial update (name only)</t>
         </is>
       </c>
       <c r="D302" s="5" t="inlineStr">
@@ -16268,7 +16268,7 @@
       </c>
       <c r="C303" s="8" t="inlineStr">
         <is>
-          <t>POST /analyze — 409 on duplicate analysis</t>
+          <t>POST /analyze â€” 409 on duplicate analysis</t>
         </is>
       </c>
       <c r="D303" s="8" t="inlineStr">
@@ -16372,7 +16372,7 @@
       </c>
       <c r="C305" s="8" t="inlineStr">
         <is>
-          <t>GET /results-img — correct Content-Type image/png</t>
+          <t>GET /results-img â€” correct Content-Type image/png</t>
         </is>
       </c>
       <c r="D305" s="8" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C306" s="5" t="inlineStr">
         <is>
-          <t>POST /upload — patient name stored in DB</t>
+          <t>POST /upload â€” patient name stored in DB</t>
         </is>
       </c>
       <c r="D306" s="5" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="C307" s="8" t="inlineStr">
         <is>
-          <t>POST /analyze — report.json created</t>
+          <t>POST /analyze â€” report.json created</t>
         </is>
       </c>
       <c r="D307" s="8" t="inlineStr">
@@ -16528,7 +16528,7 @@
       </c>
       <c r="C308" s="5" t="inlineStr">
         <is>
-          <t>GET /export-dicom — 404 for invalid scan_id</t>
+          <t>GET /export-dicom â€” 404 for invalid scan_id</t>
         </is>
       </c>
       <c r="D308" s="5" t="inlineStr">
@@ -16580,7 +16580,7 @@
       </c>
       <c r="C309" s="8" t="inlineStr">
         <is>
-          <t>POST /signup — name trimmed of whitespace</t>
+          <t>POST /signup â€” name trimmed of whitespace</t>
         </is>
       </c>
       <c r="D309" s="8" t="inlineStr">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="C310" s="5" t="inlineStr">
         <is>
-          <t>POST /login — case insensitive email</t>
+          <t>POST /login â€” case insensitive email</t>
         </is>
       </c>
       <c r="D310" s="5" t="inlineStr">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="C311" s="8" t="inlineStr">
         <is>
-          <t>POST /fetch_profile — includes credential count</t>
+          <t>POST /fetch_profile â€” includes credential count</t>
         </is>
       </c>
       <c r="D311" s="8" t="inlineStr">
@@ -16736,7 +16736,7 @@
       </c>
       <c r="C312" s="5" t="inlineStr">
         <is>
-          <t>POST /analyze — status field in response</t>
+          <t>POST /analyze â€” status field in response</t>
         </is>
       </c>
       <c r="D312" s="5" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="C313" s="8" t="inlineStr">
         <is>
-          <t>GET /scans — sorted by created_at descending</t>
+          <t>GET /scans â€” sorted by created_at descending</t>
         </is>
       </c>
       <c r="D313" s="8" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="C314" s="5" t="inlineStr">
         <is>
-          <t>POST /login — response JSON not HTML</t>
+          <t>POST /login â€” response JSON not HTML</t>
         </is>
       </c>
       <c r="D314" s="5" t="inlineStr">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="C315" s="8" t="inlineStr">
         <is>
-          <t>POST /signup — duplicate license number rejected</t>
+          <t>POST /signup â€” duplicate license number rejected</t>
         </is>
       </c>
       <c r="D315" s="8" t="inlineStr">
@@ -16944,7 +16944,7 @@
       </c>
       <c r="C316" s="5" t="inlineStr">
         <is>
-          <t>POST /upload — large ZIP (50MB) performance</t>
+          <t>POST /upload â€” large ZIP (50MB) performance</t>
         </is>
       </c>
       <c r="D316" s="5" t="inlineStr">
@@ -16996,7 +16996,7 @@
       </c>
       <c r="C317" s="8" t="inlineStr">
         <is>
-          <t>POST /analyze — measurements in report</t>
+          <t>POST /analyze â€” measurements in report</t>
         </is>
       </c>
       <c r="D317" s="8" t="inlineStr">
@@ -17048,7 +17048,7 @@
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
-          <t>GET /stl/{id} — file size &gt; 0</t>
+          <t>GET /stl/{id} â€” file size &gt; 0</t>
         </is>
       </c>
       <c r="D318" s="5" t="inlineStr">
@@ -17100,7 +17100,7 @@
       </c>
       <c r="C319" s="8" t="inlineStr">
         <is>
-          <t>POST /forgot-password — rate limit 3/min</t>
+          <t>POST /forgot-password â€” rate limit 3/min</t>
         </is>
       </c>
       <c r="D319" s="8" t="inlineStr">
@@ -17152,7 +17152,7 @@
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>POST /login — rate limit 5/min</t>
+          <t>POST /login â€” rate limit 5/min</t>
         </is>
       </c>
       <c r="D320" s="5" t="inlineStr">
@@ -17204,7 +17204,7 @@
       </c>
       <c r="C321" s="8" t="inlineStr">
         <is>
-          <t>GET /scans — includes file path field</t>
+          <t>GET /scans â€” includes file path field</t>
         </is>
       </c>
       <c r="D321" s="8" t="inlineStr">
@@ -17256,7 +17256,7 @@
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>POST /update_profile — 200 on success</t>
+          <t>POST /update_profile â€” 200 on success</t>
         </is>
       </c>
       <c r="D322" s="5" t="inlineStr">
@@ -17308,7 +17308,7 @@
       </c>
       <c r="C323" s="8" t="inlineStr">
         <is>
-          <t>POST /add_credential — credential visible in fetch</t>
+          <t>POST /add_credential â€” credential visible in fetch</t>
         </is>
       </c>
       <c r="D323" s="8" t="inlineStr">
@@ -17360,7 +17360,7 @@
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>POST /analyze — 422 on non-integer scan_id</t>
+          <t>POST /analyze â€” 422 on non-integer scan_id</t>
         </is>
       </c>
       <c r="D324" s="5" t="inlineStr">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="C325" s="8" t="inlineStr">
         <is>
-          <t>GET /stl-region — 404 for missing scan</t>
+          <t>GET /stl-region â€” 404 for missing scan</t>
         </is>
       </c>
       <c r="D325" s="8" t="inlineStr">
@@ -17464,7 +17464,7 @@
       </c>
       <c r="C326" s="5" t="inlineStr">
         <is>
-          <t>POST /reset-password — 200 on success</t>
+          <t>POST /reset-password â€” 200 on success</t>
         </is>
       </c>
       <c r="D326" s="5" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="C327" s="8" t="inlineStr">
         <is>
-          <t>POST /change_password — 200 on success</t>
+          <t>POST /change_password â€” 200 on success</t>
         </is>
       </c>
       <c r="D327" s="8" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="C328" s="5" t="inlineStr">
         <is>
-          <t>GET /results-img — no system paths in response</t>
+          <t>GET /results-img â€” no system paths in response</t>
         </is>
       </c>
       <c r="D328" s="5" t="inlineStr">
@@ -17620,7 +17620,7 @@
       </c>
       <c r="C329" s="8" t="inlineStr">
         <is>
-          <t>POST /signup — response has doctor id</t>
+          <t>POST /signup â€” response has doctor id</t>
         </is>
       </c>
       <c r="D329" s="8" t="inlineStr">
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C330" s="5" t="inlineStr">
         <is>
-          <t>POST /upload — same scan uploaded twice gets unique ids</t>
+          <t>POST /upload â€” same scan uploaded twice gets unique ids</t>
         </is>
       </c>
       <c r="D330" s="5" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="C331" s="8" t="inlineStr">
         <is>
-          <t>POST /analyze — analysis stored in DB</t>
+          <t>POST /analyze â€” analysis stored in DB</t>
         </is>
       </c>
       <c r="D331" s="8" t="inlineStr">
@@ -17776,7 +17776,7 @@
       </c>
       <c r="C332" s="5" t="inlineStr">
         <is>
-          <t>GET /scans — returns paginated or limited list</t>
+          <t>GET /scans â€” returns paginated or limited list</t>
         </is>
       </c>
       <c r="D332" s="5" t="inlineStr">
@@ -17828,7 +17828,7 @@
       </c>
       <c r="C333" s="8" t="inlineStr">
         <is>
-          <t>Full workflow: signup → upload → analyze → STL → export</t>
+          <t>Full workflow: signup â†’ upload â†’ analyze â†’ STL â†’ export</t>
         </is>
       </c>
       <c r="D333" s="8" t="inlineStr">
@@ -17880,7 +17880,7 @@
       </c>
       <c r="C334" s="5" t="inlineStr">
         <is>
-          <t>Baseline — 100 VUs login RPS ≥ 50</t>
+          <t>Baseline â€” 100 VUs login RPS â‰¥ 50</t>
         </is>
       </c>
       <c r="D334" s="5" t="inlineStr">
@@ -17905,7 +17905,7 @@
       </c>
       <c r="H334" s="5" t="inlineStr">
         <is>
-          <t>Login RPS ≥ 50 req/sec</t>
+          <t>Login RPS â‰¥ 50 req/sec</t>
         </is>
       </c>
       <c r="I334" s="6" t="inlineStr">
@@ -17932,7 +17932,7 @@
       </c>
       <c r="C335" s="8" t="inlineStr">
         <is>
-          <t>Baseline — P95 response time &lt; 2s</t>
+          <t>Baseline â€” P95 response time &lt; 2s</t>
         </is>
       </c>
       <c r="D335" s="8" t="inlineStr">
@@ -17984,7 +17984,7 @@
       </c>
       <c r="C336" s="5" t="inlineStr">
         <is>
-          <t>Baseline — error rate &lt; 5%</t>
+          <t>Baseline â€” error rate &lt; 5%</t>
         </is>
       </c>
       <c r="D336" s="5" t="inlineStr">
@@ -18036,7 +18036,7 @@
       </c>
       <c r="C337" s="8" t="inlineStr">
         <is>
-          <t>Baseline — GET /health P95 &lt; 50ms</t>
+          <t>Baseline â€” GET /health P95 &lt; 50ms</t>
         </is>
       </c>
       <c r="D337" s="8" t="inlineStr">
@@ -18088,7 +18088,7 @@
       </c>
       <c r="C338" s="5" t="inlineStr">
         <is>
-          <t>Stress 200 VUs — error rate &lt; 20%</t>
+          <t>Stress 200 VUs â€” error rate &lt; 20%</t>
         </is>
       </c>
       <c r="D338" s="5" t="inlineStr">
@@ -18140,7 +18140,7 @@
       </c>
       <c r="C339" s="8" t="inlineStr">
         <is>
-          <t>Stress 500 VUs — application stays up</t>
+          <t>Stress 500 VUs â€” application stays up</t>
         </is>
       </c>
       <c r="D339" s="8" t="inlineStr">
@@ -18192,7 +18192,7 @@
       </c>
       <c r="C340" s="5" t="inlineStr">
         <is>
-          <t>Stress 1000 VUs — health still responds</t>
+          <t>Stress 1000 VUs â€” health still responds</t>
         </is>
       </c>
       <c r="D340" s="5" t="inlineStr">
@@ -18269,7 +18269,7 @@
       </c>
       <c r="H341" s="8" t="inlineStr">
         <is>
-          <t>Failure point documented (~300–350 VUs)</t>
+          <t>Failure point documented (~300â€“350 VUs)</t>
         </is>
       </c>
       <c r="I341" s="6" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="C342" s="5" t="inlineStr">
         <is>
-          <t>Spike test — recovery within 60s</t>
+          <t>Spike test â€” recovery within 60s</t>
         </is>
       </c>
       <c r="D342" s="5" t="inlineStr">
@@ -18311,7 +18311,7 @@
       </c>
       <c r="F342" s="5" t="inlineStr">
         <is>
-          <t>50→500 VU spike; measure recovery time</t>
+          <t>50â†’500 VU spike; measure recovery time</t>
         </is>
       </c>
       <c r="G342" s="5" t="inlineStr">
@@ -18348,7 +18348,7 @@
       </c>
       <c r="C343" s="8" t="inlineStr">
         <is>
-          <t>Spike test — max error rate during spike &lt; 80%</t>
+          <t>Spike test â€” max error rate during spike &lt; 80%</t>
         </is>
       </c>
       <c r="D343" s="8" t="inlineStr">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="C344" s="5" t="inlineStr">
         <is>
-          <t>Endurance — no memory leak over 30min</t>
+          <t>Endurance â€” no memory leak over 30min</t>
         </is>
       </c>
       <c r="D344" s="5" t="inlineStr">
@@ -18452,7 +18452,7 @@
       </c>
       <c r="C345" s="8" t="inlineStr">
         <is>
-          <t>Endurance — P95 stays &lt; 5s at 30min</t>
+          <t>Endurance â€” P95 stays &lt; 5s at 30min</t>
         </is>
       </c>
       <c r="D345" s="8" t="inlineStr">
@@ -18504,7 +18504,7 @@
       </c>
       <c r="C346" s="5" t="inlineStr">
         <is>
-          <t>POST /analyze — response within 120s</t>
+          <t>POST /analyze â€” response within 120s</t>
         </is>
       </c>
       <c r="D346" s="5" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="C348" s="5" t="inlineStr">
         <is>
-          <t>POST /login with connection pool — P95 &lt; 300ms</t>
+          <t>POST /login with connection pool â€” P95 &lt; 300ms</t>
         </is>
       </c>
       <c r="D348" s="5" t="inlineStr">
@@ -18660,7 +18660,7 @@
       </c>
       <c r="C349" s="8" t="inlineStr">
         <is>
-          <t>GET /scans — response &lt; 500ms</t>
+          <t>GET /scans â€” response &lt; 500ms</t>
         </is>
       </c>
       <c r="D349" s="8" t="inlineStr">
@@ -18712,7 +18712,7 @@
       </c>
       <c r="C350" s="5" t="inlineStr">
         <is>
-          <t>10 concurrent analyses — server survives</t>
+          <t>10 concurrent analyses â€” server survives</t>
         </is>
       </c>
       <c r="D350" s="5" t="inlineStr">
@@ -18764,7 +18764,7 @@
       </c>
       <c r="C351" s="8" t="inlineStr">
         <is>
-          <t>Baseline — verify MySQL connection count</t>
+          <t>Baseline â€” verify MySQL connection count</t>
         </is>
       </c>
       <c r="D351" s="8" t="inlineStr">
@@ -18789,7 +18789,7 @@
       </c>
       <c r="H351" s="8" t="inlineStr">
         <is>
-          <t>Active connections ≤ configured pool size</t>
+          <t>Active connections â‰¤ configured pool size</t>
         </is>
       </c>
       <c r="I351" s="9" t="inlineStr">
@@ -18816,7 +18816,7 @@
       </c>
       <c r="C352" s="5" t="inlineStr">
         <is>
-          <t>POST /login — no degradation over 1000 requests</t>
+          <t>POST /login â€” no degradation over 1000 requests</t>
         </is>
       </c>
       <c r="D352" s="5" t="inlineStr">
@@ -18841,7 +18841,7 @@
       </c>
       <c r="H352" s="5" t="inlineStr">
         <is>
-          <t>Latency stable ±10% from start to end</t>
+          <t>Latency stable Â±10% from start to end</t>
         </is>
       </c>
       <c r="I352" s="6" t="inlineStr">
@@ -18868,7 +18868,7 @@
       </c>
       <c r="C353" s="8" t="inlineStr">
         <is>
-          <t>Rate limiter tested — 429 returned promptly</t>
+          <t>Rate limiter tested â€” 429 returned promptly</t>
         </is>
       </c>
       <c r="D353" s="8" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="C354" s="5" t="inlineStr">
         <is>
-          <t>GET /health — 1000 RPS sustained</t>
+          <t>GET /health â€” 1000 RPS sustained</t>
         </is>
       </c>
       <c r="D354" s="5" t="inlineStr">
@@ -18945,7 +18945,7 @@
       </c>
       <c r="H354" s="5" t="inlineStr">
         <is>
-          <t>Throughput ≥ 500 RPS</t>
+          <t>Throughput â‰¥ 500 RPS</t>
         </is>
       </c>
       <c r="I354" s="7" t="inlineStr">
@@ -19232,7 +19232,7 @@
       </c>
       <c r="C360" s="5" t="inlineStr">
         <is>
-          <t>Endurance — error rate stays &lt; 15% at 30min</t>
+          <t>Endurance â€” error rate stays &lt; 15% at 30min</t>
         </is>
       </c>
       <c r="D360" s="5" t="inlineStr">
@@ -19336,7 +19336,7 @@
       </c>
       <c r="C362" s="5" t="inlineStr">
         <is>
-          <t>Baseline — avg response time &lt; 500ms</t>
+          <t>Baseline â€” avg response time &lt; 500ms</t>
         </is>
       </c>
       <c r="D362" s="5" t="inlineStr">
@@ -19388,7 +19388,7 @@
       </c>
       <c r="C363" s="8" t="inlineStr">
         <is>
-          <t>With connection pool — baseline error rate &lt; 1%</t>
+          <t>With connection pool â€” baseline error rate &lt; 1%</t>
         </is>
       </c>
       <c r="D363" s="8" t="inlineStr">
@@ -19440,7 +19440,7 @@
       </c>
       <c r="C364" s="5" t="inlineStr">
         <is>
-          <t>GET /scans — unauthenticated returns data</t>
+          <t>GET /scans â€” unauthenticated returns data</t>
         </is>
       </c>
       <c r="D364" s="5" t="inlineStr">
@@ -19492,7 +19492,7 @@
       </c>
       <c r="C365" s="8" t="inlineStr">
         <is>
-          <t>GET /stl/1 — unauthenticated download</t>
+          <t>GET /stl/1 â€” unauthenticated download</t>
         </is>
       </c>
       <c r="D365" s="8" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C366" s="5" t="inlineStr">
         <is>
-          <t>POST /login — 100 requests no lockout</t>
+          <t>POST /login â€” 100 requests no lockout</t>
         </is>
       </c>
       <c r="D366" s="5" t="inlineStr">
@@ -19569,7 +19569,7 @@
       </c>
       <c r="H366" s="5" t="inlineStr">
         <is>
-          <t>Never blocked — all return 200 (VULNERABILITY)</t>
+          <t>Never blocked â€” all return 200 (VULNERABILITY)</t>
         </is>
       </c>
       <c r="I366" s="10" t="inlineStr">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C367" s="8" t="inlineStr">
         <is>
-          <t>POST /forgot-password — token in response</t>
+          <t>POST /forgot-password â€” token in response</t>
         </is>
       </c>
       <c r="D367" s="8" t="inlineStr">
@@ -19648,7 +19648,7 @@
       </c>
       <c r="C368" s="5" t="inlineStr">
         <is>
-          <t>GET /results-img — path traversal read</t>
+          <t>GET /results-img â€” path traversal read</t>
         </is>
       </c>
       <c r="D368" s="5" t="inlineStr">
@@ -19700,7 +19700,7 @@
       </c>
       <c r="C369" s="8" t="inlineStr">
         <is>
-          <t>GET /volume-test — unauthenticated debug</t>
+          <t>GET /volume-test â€” unauthenticated debug</t>
         </is>
       </c>
       <c r="D369" s="8" t="inlineStr">
@@ -19752,7 +19752,7 @@
       </c>
       <c r="C370" s="5" t="inlineStr">
         <is>
-          <t>CORS — evil origin reflected</t>
+          <t>CORS â€” evil origin reflected</t>
         </is>
       </c>
       <c r="D370" s="5" t="inlineStr">
@@ -19804,7 +19804,7 @@
       </c>
       <c r="C371" s="8" t="inlineStr">
         <is>
-          <t>POST /fetch_profile — IDOR doctor id=2 as doctor 1</t>
+          <t>POST /fetch_profile â€” IDOR doctor id=2 as doctor 1</t>
         </is>
       </c>
       <c r="D371" s="8" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="C372" s="5" t="inlineStr">
         <is>
-          <t>POST /analyze — IDOR any scan_id</t>
+          <t>POST /analyze â€” IDOR any scan_id</t>
         </is>
       </c>
       <c r="D372" s="5" t="inlineStr">
@@ -19908,7 +19908,7 @@
       </c>
       <c r="C373" s="8" t="inlineStr">
         <is>
-          <t>Security headers absent — X-Frame-Options</t>
+          <t>Security headers absent â€” X-Frame-Options</t>
         </is>
       </c>
       <c r="D373" s="8" t="inlineStr">
@@ -19960,7 +19960,7 @@
       </c>
       <c r="C374" s="5" t="inlineStr">
         <is>
-          <t>Security headers absent — CSP</t>
+          <t>Security headers absent â€” CSP</t>
         </is>
       </c>
       <c r="D374" s="5" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="C375" s="8" t="inlineStr">
         <is>
-          <t>Security headers absent — HSTS</t>
+          <t>Security headers absent â€” HSTS</t>
         </is>
       </c>
       <c r="D375" s="8" t="inlineStr">
@@ -20116,7 +20116,7 @@
       </c>
       <c r="C377" s="8" t="inlineStr">
         <is>
-          <t>POST /upload — no auth required</t>
+          <t>POST /upload â€” no auth required</t>
         </is>
       </c>
       <c r="D377" s="8" t="inlineStr">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="H377" s="8" t="inlineStr">
         <is>
-          <t>HTTP 422 (validation) not 401 — no auth gate (VULNERABILITY)</t>
+          <t>HTTP 422 (validation) not 401 â€” no auth gate (VULNERABILITY)</t>
         </is>
       </c>
       <c r="I377" s="10" t="inlineStr">
@@ -20168,7 +20168,7 @@
       </c>
       <c r="C378" s="5" t="inlineStr">
         <is>
-          <t>POST /update_profile — IDOR update</t>
+          <t>POST /update_profile â€” IDOR update</t>
         </is>
       </c>
       <c r="D378" s="5" t="inlineStr">
@@ -20220,7 +20220,7 @@
       </c>
       <c r="C379" s="8" t="inlineStr">
         <is>
-          <t>POST /change_password — IDOR</t>
+          <t>POST /change_password â€” IDOR</t>
         </is>
       </c>
       <c r="D379" s="8" t="inlineStr">
@@ -20272,7 +20272,7 @@
       </c>
       <c r="C380" s="5" t="inlineStr">
         <is>
-          <t>GET /export-dicom — unauthenticated</t>
+          <t>GET /export-dicom â€” unauthenticated</t>
         </is>
       </c>
       <c r="D380" s="5" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="C381" s="8" t="inlineStr">
         <is>
-          <t>POST /add_credential — IDOR</t>
+          <t>POST /add_credential â€” IDOR</t>
         </is>
       </c>
       <c r="D381" s="8" t="inlineStr">
@@ -20376,7 +20376,7 @@
       </c>
       <c r="C382" s="5" t="inlineStr">
         <is>
-          <t>GET /results-img — no auth</t>
+          <t>GET /results-img â€” no auth</t>
         </is>
       </c>
       <c r="D382" s="5" t="inlineStr">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="C383" s="8" t="inlineStr">
         <is>
-          <t>POST /login — response exposes doctor id</t>
+          <t>POST /login â€” response exposes doctor id</t>
         </is>
       </c>
       <c r="D383" s="8" t="inlineStr">
@@ -20480,7 +20480,7 @@
       </c>
       <c r="C384" s="5" t="inlineStr">
         <is>
-          <t>JWT — tampered payload accepted</t>
+          <t>JWT â€” tampered payload accepted</t>
         </is>
       </c>
       <c r="D384" s="5" t="inlineStr">
@@ -20609,7 +20609,7 @@
       </c>
       <c r="H386" s="5" t="inlineStr">
         <is>
-          <t>Returns 404 — PASS or 200 file content — FAIL</t>
+          <t>Returns 404 â€” PASS or 200 file content â€” FAIL</t>
         </is>
       </c>
       <c r="I386" s="10" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="C389" s="8" t="inlineStr">
         <is>
-          <t>POST /upload — filename path traversal executed</t>
+          <t>POST /upload â€” filename path traversal executed</t>
         </is>
       </c>
       <c r="D389" s="8" t="inlineStr">
@@ -20792,7 +20792,7 @@
       </c>
       <c r="C390" s="5" t="inlineStr">
         <is>
-          <t>POST /signup — no rate limit on registration</t>
+          <t>POST /signup â€” no rate limit on registration</t>
         </is>
       </c>
       <c r="D390" s="5" t="inlineStr">
@@ -20844,7 +20844,7 @@
       </c>
       <c r="C391" s="8" t="inlineStr">
         <is>
-          <t>GET /scans — response contains full file paths</t>
+          <t>GET /scans â€” response contains full file paths</t>
         </is>
       </c>
       <c r="D391" s="8" t="inlineStr">
@@ -20896,7 +20896,7 @@
       </c>
       <c r="C392" s="5" t="inlineStr">
         <is>
-          <t>POST /login — timing difference reveals valid emails</t>
+          <t>POST /login â€” timing difference reveals valid emails</t>
         </is>
       </c>
       <c r="D392" s="5" t="inlineStr">
@@ -20948,7 +20948,7 @@
       </c>
       <c r="C393" s="8" t="inlineStr">
         <is>
-          <t>POST /fetch_credentials — IDOR any doctor_id</t>
+          <t>POST /fetch_credentials â€” IDOR any doctor_id</t>
         </is>
       </c>
       <c r="D393" s="8" t="inlineStr">
@@ -21104,7 +21104,7 @@
       </c>
       <c r="C396" s="5" t="inlineStr">
         <is>
-          <t>POST /analyze — no ownership check on scan</t>
+          <t>POST /analyze â€” no ownership check on scan</t>
         </is>
       </c>
       <c r="D396" s="5" t="inlineStr">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="C397" s="8" t="inlineStr">
         <is>
-          <t>GET /stl-region — unauthenticated</t>
+          <t>GET /stl-region â€” unauthenticated</t>
         </is>
       </c>
       <c r="D397" s="8" t="inlineStr">
@@ -21208,7 +21208,7 @@
       </c>
       <c r="C398" s="5" t="inlineStr">
         <is>
-          <t>POST /reset-password — token valid for 24h+</t>
+          <t>POST /reset-password â€” token valid for 24h+</t>
         </is>
       </c>
       <c r="D398" s="5" t="inlineStr">
@@ -21260,7 +21260,7 @@
       </c>
       <c r="C399" s="8" t="inlineStr">
         <is>
-          <t>GET /health — reveals app version</t>
+          <t>GET /health â€” reveals app version</t>
         </is>
       </c>
       <c r="D399" s="8" t="inlineStr">
@@ -21312,7 +21312,7 @@
       </c>
       <c r="C400" s="5" t="inlineStr">
         <is>
-          <t>POST /login — no account lockout after 50 fails</t>
+          <t>POST /login â€” no account lockout after 50 fails</t>
         </is>
       </c>
       <c r="D400" s="5" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="C401" s="8" t="inlineStr">
         <is>
-          <t>POST /upload — ZIP extraction runs as server user</t>
+          <t>POST /upload â€” ZIP extraction runs as server user</t>
         </is>
       </c>
       <c r="D401" s="8" t="inlineStr">
@@ -21535,7 +21535,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Test Cases — Summary by Category</t>
+          <t>Test Cases â€” Summary by Category</t>
         </is>
       </c>
     </row>
